--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/179.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/179.xlsx
@@ -426,13 +426,13 @@
         <v>-2.658722952555626</v>
       </c>
       <c r="E2">
-        <v>-11.62038337357028</v>
+        <v>-11.93015363806497</v>
       </c>
       <c r="F2">
-        <v>2.928186864351733</v>
+        <v>1.991511919194649</v>
       </c>
       <c r="G2">
-        <v>-13.12947247432306</v>
+        <v>-15.21345261493042</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.811568833416001</v>
       </c>
       <c r="E3">
-        <v>-12.29398029678922</v>
+        <v>-11.27634161778554</v>
       </c>
       <c r="F3">
-        <v>2.988221988194212</v>
+        <v>2.418762517355987</v>
       </c>
       <c r="G3">
-        <v>-13.36982470156522</v>
+        <v>-13.17320809144237</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.9272899745683</v>
       </c>
       <c r="E4">
-        <v>-12.25753513797549</v>
+        <v>-11.73858560211849</v>
       </c>
       <c r="F4">
-        <v>3.131864114724569</v>
+        <v>2.490958918923126</v>
       </c>
       <c r="G4">
-        <v>-12.34808772123442</v>
+        <v>-13.17096685211228</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.990555223739006</v>
       </c>
       <c r="E5">
-        <v>-12.49158478858792</v>
+        <v>-11.53447369317076</v>
       </c>
       <c r="F5">
-        <v>3.212987866537039</v>
+        <v>2.88757906097395</v>
       </c>
       <c r="G5">
-        <v>-12.12557933444892</v>
+        <v>-13.58768011659527</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.99905051856906</v>
       </c>
       <c r="E6">
-        <v>-13.93641253463118</v>
+        <v>-14.08707486486637</v>
       </c>
       <c r="F6">
-        <v>3.503521884136237</v>
+        <v>2.782045649886812</v>
       </c>
       <c r="G6">
-        <v>-10.75625824631342</v>
+        <v>-12.3658984562357</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.951834792985868</v>
       </c>
       <c r="E7">
-        <v>-14.84179487145872</v>
+        <v>-12.97354574875027</v>
       </c>
       <c r="F7">
-        <v>3.559235074535481</v>
+        <v>2.823434220280906</v>
       </c>
       <c r="G7">
-        <v>-11.27651047780988</v>
+        <v>-12.62561075379152</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.848809959741732</v>
       </c>
       <c r="E8">
-        <v>-15.42263053310455</v>
+        <v>-15.5932815476096</v>
       </c>
       <c r="F8">
-        <v>3.790359532128799</v>
+        <v>3.173238431765425</v>
       </c>
       <c r="G8">
-        <v>-9.931323266655664</v>
+        <v>-10.76596476583456</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.69298876521697</v>
       </c>
       <c r="E9">
-        <v>-15.05274024768402</v>
+        <v>-15.82392578576826</v>
       </c>
       <c r="F9">
-        <v>3.770830854485515</v>
+        <v>3.606606885878106</v>
       </c>
       <c r="G9">
-        <v>-9.736875063861032</v>
+        <v>-10.63334431153135</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.487613752110692</v>
       </c>
       <c r="E10">
-        <v>-17.23016187631815</v>
+        <v>-15.7013852791207</v>
       </c>
       <c r="F10">
-        <v>3.806914010062887</v>
+        <v>3.334122364597172</v>
       </c>
       <c r="G10">
-        <v>-8.282714625190623</v>
+        <v>-10.35088194502966</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.238116028903081</v>
       </c>
       <c r="E11">
-        <v>-16.70045268621893</v>
+        <v>-16.99561862203888</v>
       </c>
       <c r="F11">
-        <v>4.121982799704073</v>
+        <v>3.564714697002902</v>
       </c>
       <c r="G11">
-        <v>-7.472524815364786</v>
+        <v>-9.196150418749712</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.954624645233071</v>
       </c>
       <c r="E12">
-        <v>-18.78474171841131</v>
+        <v>-18.24516951192338</v>
       </c>
       <c r="F12">
-        <v>3.972425531579549</v>
+        <v>3.265460794633295</v>
       </c>
       <c r="G12">
-        <v>-6.634731676832505</v>
+        <v>-8.206449587602433</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.645441525415961</v>
       </c>
       <c r="E13">
-        <v>-18.37842438807309</v>
+        <v>-16.46547922690893</v>
       </c>
       <c r="F13">
-        <v>4.357783940865684</v>
+        <v>3.569814230050617</v>
       </c>
       <c r="G13">
-        <v>-6.49589732855209</v>
+        <v>-7.071885904747726</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.32532788499398</v>
       </c>
       <c r="E14">
-        <v>-20.12693160107072</v>
+        <v>-17.65290851035621</v>
       </c>
       <c r="F14">
-        <v>4.241067982309627</v>
+        <v>3.564252254875594</v>
       </c>
       <c r="G14">
-        <v>-5.56247908211796</v>
+        <v>-7.376303809265869</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.002359808339974</v>
       </c>
       <c r="E15">
-        <v>-20.31423381450197</v>
+        <v>-18.67399335807972</v>
       </c>
       <c r="F15">
-        <v>4.644846475098237</v>
+        <v>3.92662475650504</v>
       </c>
       <c r="G15">
-        <v>-5.539864745539199</v>
+        <v>-6.524533547466786</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.6855360631318709</v>
       </c>
       <c r="E16">
-        <v>-21.49448093817308</v>
+        <v>-22.20140290161447</v>
       </c>
       <c r="F16">
-        <v>4.852642944557132</v>
+        <v>3.86325276429873</v>
       </c>
       <c r="G16">
-        <v>-5.616480700954552</v>
+        <v>-4.316018960035887</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.3786455048506945</v>
       </c>
       <c r="E17">
-        <v>-22.06627323722559</v>
+        <v>-21.33881464415942</v>
       </c>
       <c r="F17">
-        <v>4.834349557527891</v>
+        <v>4.131774853379235</v>
       </c>
       <c r="G17">
-        <v>-4.805850588571992</v>
+        <v>-5.372851033628507</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.0839191219420078</v>
       </c>
       <c r="E18">
-        <v>-23.1054176392917</v>
+        <v>-21.11730433807422</v>
       </c>
       <c r="F18">
-        <v>5.289980165693905</v>
+        <v>4.188344828678732</v>
       </c>
       <c r="G18">
-        <v>-4.712668663278126</v>
+        <v>-5.249417343196781</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.1936081671470429</v>
       </c>
       <c r="E19">
-        <v>-24.04099584080239</v>
+        <v>-23.13065482493645</v>
       </c>
       <c r="F19">
-        <v>5.253664205346962</v>
+        <v>4.540141342204874</v>
       </c>
       <c r="G19">
-        <v>-4.721653483871707</v>
+        <v>-4.926950344398532</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.4488435455388061</v>
       </c>
       <c r="E20">
-        <v>-24.58731094508774</v>
+        <v>-23.96754399239797</v>
       </c>
       <c r="F20">
-        <v>5.257514194427396</v>
+        <v>4.606853370186845</v>
       </c>
       <c r="G20">
-        <v>-4.092471061951061</v>
+        <v>-4.543850704048531</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.668016306213732</v>
       </c>
       <c r="E21">
-        <v>-24.38246995182478</v>
+        <v>-24.68211454843832</v>
       </c>
       <c r="F21">
-        <v>5.381383752603492</v>
+        <v>4.042735739401398</v>
       </c>
       <c r="G21">
-        <v>-4.550739949315754</v>
+        <v>-3.714856995559633</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.8361254992380467</v>
       </c>
       <c r="E22">
-        <v>-26.12900275015507</v>
+        <v>-24.96605439719326</v>
       </c>
       <c r="F22">
-        <v>5.418683194323922</v>
+        <v>4.187302750186373</v>
       </c>
       <c r="G22">
-        <v>-4.199964475611196</v>
+        <v>-3.412475076548142</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.9345714582925065</v>
       </c>
       <c r="E23">
-        <v>-25.8370792017246</v>
+        <v>-25.14537291094899</v>
       </c>
       <c r="F23">
-        <v>5.096017367406374</v>
+        <v>4.612880954901008</v>
       </c>
       <c r="G23">
-        <v>-3.104246734114298</v>
+        <v>-3.765594416494503</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.9491321989036283</v>
       </c>
       <c r="E24">
-        <v>-25.18380606985209</v>
+        <v>-27.05550136128037</v>
       </c>
       <c r="F24">
-        <v>5.647997476055892</v>
+        <v>3.97172711727084</v>
       </c>
       <c r="G24">
-        <v>-3.159615608258608</v>
+        <v>-3.496483480152687</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.8682385635169406</v>
       </c>
       <c r="E25">
-        <v>-27.1422442808973</v>
+        <v>-25.5786029623148</v>
       </c>
       <c r="F25">
-        <v>5.04650596937199</v>
+        <v>3.558088471452703</v>
       </c>
       <c r="G25">
-        <v>-3.167776103012912</v>
+        <v>-3.114085675457011</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.6895541694886935</v>
       </c>
       <c r="E26">
-        <v>-26.87045885637895</v>
+        <v>-26.35116515649737</v>
       </c>
       <c r="F26">
-        <v>4.91692873507665</v>
+        <v>4.036891864573427</v>
       </c>
       <c r="G26">
-        <v>-2.75388176805661</v>
+        <v>-3.344870426090685</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.4136581547776091</v>
       </c>
       <c r="E27">
-        <v>-27.11697992440851</v>
+        <v>-25.741080081236</v>
       </c>
       <c r="F27">
-        <v>4.76014343315406</v>
+        <v>3.63017084619393</v>
       </c>
       <c r="G27">
-        <v>-2.618616187867528</v>
+        <v>-4.263371354324858</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.05161156639500426</v>
       </c>
       <c r="E28">
-        <v>-27.10065024713685</v>
+        <v>-24.69710379740371</v>
       </c>
       <c r="F28">
-        <v>4.89882222534543</v>
+        <v>4.03912013879645</v>
       </c>
       <c r="G28">
-        <v>-2.979439167283774</v>
+        <v>-2.428031391717226</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.3818096523039338</v>
       </c>
       <c r="E29">
-        <v>-26.85490807663661</v>
+        <v>-25.58762821101208</v>
       </c>
       <c r="F29">
-        <v>5.005763550991395</v>
+        <v>3.723805874738372</v>
       </c>
       <c r="G29">
-        <v>-2.808224373083747</v>
+        <v>-3.474220061401089</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.8667520090544207</v>
       </c>
       <c r="E30">
-        <v>-25.75970569482955</v>
+        <v>-25.72277146082299</v>
       </c>
       <c r="F30">
-        <v>4.50928124873662</v>
+        <v>3.437175692220732</v>
       </c>
       <c r="G30">
-        <v>-3.187804903525502</v>
+        <v>-3.353156721575481</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.378579426373051</v>
       </c>
       <c r="E31">
-        <v>-25.18028744554812</v>
+        <v>-25.36810137654225</v>
       </c>
       <c r="F31">
-        <v>4.804775433262974</v>
+        <v>3.576377107364198</v>
       </c>
       <c r="G31">
-        <v>-3.595518449959985</v>
+        <v>-2.300747536823327</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.896910111931702</v>
       </c>
       <c r="E32">
-        <v>-26.21951788862038</v>
+        <v>-26.53931419456805</v>
       </c>
       <c r="F32">
-        <v>4.953694467903577</v>
+        <v>3.57984225590718</v>
       </c>
       <c r="G32">
-        <v>-3.595581350325231</v>
+        <v>-3.206565765096552</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.395363114856901</v>
       </c>
       <c r="E33">
-        <v>-25.99448442975722</v>
+        <v>-24.22770482413863</v>
       </c>
       <c r="F33">
-        <v>4.690786616293305</v>
+        <v>3.934234463428727</v>
       </c>
       <c r="G33">
-        <v>-3.363435965474917</v>
+        <v>-3.556665887511098</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.859047820573053</v>
       </c>
       <c r="E34">
-        <v>-24.88323313606697</v>
+        <v>-24.13843954449944</v>
       </c>
       <c r="F34">
-        <v>4.60669183218347</v>
+        <v>3.888465362472526</v>
       </c>
       <c r="G34">
-        <v>-2.720713412298652</v>
+        <v>-2.784107048830156</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.270566799010859</v>
       </c>
       <c r="E35">
-        <v>-24.46026007832854</v>
+        <v>-23.03574253820968</v>
       </c>
       <c r="F35">
-        <v>5.124756878653853</v>
+        <v>3.902943601951474</v>
       </c>
       <c r="G35">
-        <v>-3.639687748544941</v>
+        <v>-4.75439146870956</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.622517126079395</v>
       </c>
       <c r="E36">
-        <v>-23.62883677899427</v>
+        <v>-23.04019402815922</v>
       </c>
       <c r="F36">
-        <v>4.879453501999606</v>
+        <v>4.137275064023556</v>
       </c>
       <c r="G36">
-        <v>-4.6206619816507</v>
+        <v>-4.081317834029257</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.912993375586776</v>
       </c>
       <c r="E37">
-        <v>-23.7133969741395</v>
+        <v>-22.84095928571776</v>
       </c>
       <c r="F37">
-        <v>5.202885842580227</v>
+        <v>4.16370394834041</v>
       </c>
       <c r="G37">
-        <v>-4.245325570590291</v>
+        <v>-4.612090979249527</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.142885396753181</v>
       </c>
       <c r="E38">
-        <v>-22.32573668396907</v>
+        <v>-22.37698089583987</v>
       </c>
       <c r="F38">
-        <v>5.026473673247597</v>
+        <v>4.310285433049823</v>
       </c>
       <c r="G38">
-        <v>-4.645941307388576</v>
+        <v>-5.046169710358765</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.324281520383305</v>
       </c>
       <c r="E39">
-        <v>-22.14118325426047</v>
+        <v>-20.49323080660316</v>
       </c>
       <c r="F39">
-        <v>5.048477683236712</v>
+        <v>4.802893990635432</v>
       </c>
       <c r="G39">
-        <v>-5.296357568398107</v>
+        <v>-3.977178003000403</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.463991803369132</v>
       </c>
       <c r="E40">
-        <v>-22.29936737982241</v>
+        <v>-20.95147161991333</v>
       </c>
       <c r="F40">
-        <v>5.203359370648943</v>
+        <v>4.647822258513348</v>
       </c>
       <c r="G40">
-        <v>-4.37614839866567</v>
+        <v>-6.025869383431906</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.579167699038841</v>
       </c>
       <c r="E41">
-        <v>-20.63395766486552</v>
+        <v>-18.63340464554897</v>
       </c>
       <c r="F41">
-        <v>5.524493753946262</v>
+        <v>4.733475409243975</v>
       </c>
       <c r="G41">
-        <v>-4.621966336593173</v>
+        <v>-6.316545213416534</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.680961878234849</v>
       </c>
       <c r="E42">
-        <v>-20.33784980645197</v>
+        <v>-20.18192086094586</v>
       </c>
       <c r="F42">
-        <v>5.309646625751832</v>
+        <v>5.296292817472846</v>
       </c>
       <c r="G42">
-        <v>-5.283178286606268</v>
+        <v>-5.553199622971383</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.779949548257368</v>
       </c>
       <c r="E43">
-        <v>-18.66149476981855</v>
+        <v>-19.49118819208189</v>
       </c>
       <c r="F43">
-        <v>5.367873157438878</v>
+        <v>5.215465218666563</v>
       </c>
       <c r="G43">
-        <v>-5.063291851887876</v>
+        <v>-6.73078053456338</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.886605958986824</v>
       </c>
       <c r="E44">
-        <v>-19.03887515124776</v>
+        <v>-18.85697540730766</v>
       </c>
       <c r="F44">
-        <v>5.363269324342696</v>
+        <v>5.018631161554341</v>
       </c>
       <c r="G44">
-        <v>-5.634314609774606</v>
+        <v>-6.148803181487202</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.003097713944063</v>
       </c>
       <c r="E45">
-        <v>-18.86215145309843</v>
+        <v>-18.94561122905979</v>
       </c>
       <c r="F45">
-        <v>5.5380376069351</v>
+        <v>4.879553275472279</v>
       </c>
       <c r="G45">
-        <v>-5.622482720017251</v>
+        <v>-5.854452645953983</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.134847163509097</v>
       </c>
       <c r="E46">
-        <v>-17.89838350088999</v>
+        <v>-16.98949612518051</v>
       </c>
       <c r="F46">
-        <v>5.509733614814366</v>
+        <v>4.995908149079615</v>
       </c>
       <c r="G46">
-        <v>-6.034205337099791</v>
+        <v>-6.850572624901909</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.278277738637694</v>
       </c>
       <c r="E47">
-        <v>-17.84145152566556</v>
+        <v>-16.98158488108911</v>
       </c>
       <c r="F47">
-        <v>5.745822990452587</v>
+        <v>5.142028775367636</v>
       </c>
       <c r="G47">
-        <v>-5.827246582712252</v>
+        <v>-7.285796804767734</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.433946086441894</v>
       </c>
       <c r="E48">
-        <v>-17.16591188709733</v>
+        <v>-16.18652975651044</v>
       </c>
       <c r="F48">
-        <v>5.88631037479939</v>
+        <v>5.241597949977229</v>
       </c>
       <c r="G48">
-        <v>-7.192912828572402</v>
+        <v>-7.805562386069928</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.599884761999376</v>
       </c>
       <c r="E49">
-        <v>-16.30165262273344</v>
+        <v>-17.03685490635273</v>
       </c>
       <c r="F49">
-        <v>5.770571562793159</v>
+        <v>4.961947159428932</v>
       </c>
       <c r="G49">
-        <v>-5.646136567895343</v>
+        <v>-7.776992378066018</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.772327619071635</v>
       </c>
       <c r="E50">
-        <v>-16.6246324459085</v>
+        <v>-17.02007691015431</v>
       </c>
       <c r="F50">
-        <v>5.716887099671593</v>
+        <v>4.975535356183402</v>
       </c>
       <c r="G50">
-        <v>-7.092358318362579</v>
+        <v>-6.772172285440888</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.95352308631588</v>
       </c>
       <c r="E51">
-        <v>-15.46083726830726</v>
+        <v>-17.17508657543687</v>
       </c>
       <c r="F51">
-        <v>5.724811964072452</v>
+        <v>5.17856962195457</v>
       </c>
       <c r="G51">
-        <v>-7.422982501369593</v>
+        <v>-7.797329059313761</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.139997969507605</v>
       </c>
       <c r="E52">
-        <v>-14.47749272296367</v>
+        <v>-15.73879047442406</v>
       </c>
       <c r="F52">
-        <v>5.455325398089444</v>
+        <v>5.085870563606153</v>
       </c>
       <c r="G52">
-        <v>-6.741556360293708</v>
+        <v>-7.24947680965639</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.335821798144079</v>
       </c>
       <c r="E53">
-        <v>-14.43633795118196</v>
+        <v>-15.6233958997606</v>
       </c>
       <c r="F53">
-        <v>5.859034207817776</v>
+        <v>5.302500944661369</v>
       </c>
       <c r="G53">
-        <v>-7.0453882982514</v>
+        <v>-7.390797377636798</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.539252894875771</v>
       </c>
       <c r="E54">
-        <v>-13.7733014293489</v>
+        <v>-15.03271533562211</v>
       </c>
       <c r="F54">
-        <v>5.82189313668889</v>
+        <v>4.583116785926238</v>
       </c>
       <c r="G54">
-        <v>-7.447940704190159</v>
+        <v>-7.712827384423863</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.751183007202764</v>
       </c>
       <c r="E55">
-        <v>-13.73859067608011</v>
+        <v>-13.56361949737174</v>
       </c>
       <c r="F55">
-        <v>5.650639097522845</v>
+        <v>5.056133317631947</v>
       </c>
       <c r="G55">
-        <v>-7.539755374176305</v>
+        <v>-7.547310039096923</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.970089387526557</v>
       </c>
       <c r="E56">
-        <v>-13.40721506209482</v>
+        <v>-13.33092838896161</v>
       </c>
       <c r="F56">
-        <v>5.556342079905749</v>
+        <v>5.361755301487536</v>
       </c>
       <c r="G56">
-        <v>-8.329270827109394</v>
+        <v>-7.410097858130749</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.189060406050594</v>
       </c>
       <c r="E57">
-        <v>-12.36961486966533</v>
+        <v>-12.86352647273392</v>
       </c>
       <c r="F57">
-        <v>5.726470104165917</v>
+        <v>5.021573687145227</v>
       </c>
       <c r="G57">
-        <v>-8.341218585960624</v>
+        <v>-7.502657400863233</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.405582756668798</v>
       </c>
       <c r="E58">
-        <v>-12.13717282732562</v>
+        <v>-12.9461122532118</v>
       </c>
       <c r="F58">
-        <v>5.781516554374761</v>
+        <v>5.105115757890573</v>
       </c>
       <c r="G58">
-        <v>-7.935842284676867</v>
+        <v>-9.005128630588224</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.609432582759341</v>
       </c>
       <c r="E59">
-        <v>-11.29386681219522</v>
+        <v>-11.00282178772225</v>
       </c>
       <c r="F59">
-        <v>5.817574370657487</v>
+        <v>5.101802645115474</v>
       </c>
       <c r="G59">
-        <v>-7.479281638810439</v>
+        <v>-8.527016333261141</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.795028249696023</v>
       </c>
       <c r="E60">
-        <v>-11.39982404702669</v>
+        <v>-10.16469634685662</v>
       </c>
       <c r="F60">
-        <v>5.834795588781975</v>
+        <v>4.731679486735866</v>
       </c>
       <c r="G60">
-        <v>-8.460421399193162</v>
+        <v>-8.7853911704191</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.955775459721644</v>
       </c>
       <c r="E61">
-        <v>-11.2910772722065</v>
+        <v>-9.05013926714078</v>
       </c>
       <c r="F61">
-        <v>5.610789889278558</v>
+        <v>5.159763114208727</v>
       </c>
       <c r="G61">
-        <v>-8.460573684287969</v>
+        <v>-8.404052740295992</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.082783340812318</v>
       </c>
       <c r="E62">
-        <v>-11.24741372582454</v>
+        <v>-11.52565675427783</v>
       </c>
       <c r="F62">
-        <v>5.596196039267784</v>
+        <v>5.182855130161749</v>
       </c>
       <c r="G62">
-        <v>-8.370748652170922</v>
+        <v>-9.001745253047091</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.173662819421986</v>
       </c>
       <c r="E63">
-        <v>-10.98365728572178</v>
+        <v>-10.34122079214962</v>
       </c>
       <c r="F63">
-        <v>5.745164168791764</v>
+        <v>5.174678456520335</v>
       </c>
       <c r="G63">
-        <v>-8.298340400135984</v>
+        <v>-9.197607058786991</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.221188882359778</v>
       </c>
       <c r="E64">
-        <v>-10.19740551461403</v>
+        <v>-9.920063652488263</v>
       </c>
       <c r="F64">
-        <v>5.598167753132506</v>
+        <v>5.401127814251276</v>
       </c>
       <c r="G64">
-        <v>-9.034281294607046</v>
+        <v>-8.875444630178356</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.226390361249679</v>
       </c>
       <c r="E65">
-        <v>-9.398066453624102</v>
+        <v>-10.44851845528736</v>
       </c>
       <c r="F65">
-        <v>5.475473304745665</v>
+        <v>4.849599061787657</v>
       </c>
       <c r="G65">
-        <v>-8.433096156312017</v>
+        <v>-9.677990390354015</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.1881326122261</v>
       </c>
       <c r="E66">
-        <v>-9.956685421788293</v>
+        <v>-8.728205521461486</v>
       </c>
       <c r="F66">
-        <v>5.261840878988377</v>
+        <v>4.981317466480672</v>
       </c>
       <c r="G66">
-        <v>-8.20287088787448</v>
+        <v>-8.595455241194495</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.108699649681615</v>
       </c>
       <c r="E67">
-        <v>-10.80065259412381</v>
+        <v>-9.958415298859224</v>
       </c>
       <c r="F67">
-        <v>5.012627332428909</v>
+        <v>4.575274274232982</v>
       </c>
       <c r="G67">
-        <v>-8.401361266772565</v>
+        <v>-8.429633325677941</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.994465840299245</v>
       </c>
       <c r="E68">
-        <v>-9.44242738500324</v>
+        <v>-8.502995452112025</v>
       </c>
       <c r="F68">
-        <v>5.468641197426459</v>
+        <v>4.268187362405611</v>
       </c>
       <c r="G68">
-        <v>-8.031159511843564</v>
+        <v>-8.836168317900441</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.847972299413213</v>
       </c>
       <c r="E69">
-        <v>-9.872333536447419</v>
+        <v>-10.54708974901232</v>
       </c>
       <c r="F69">
-        <v>5.086526217855145</v>
+        <v>5.011222585281915</v>
       </c>
       <c r="G69">
-        <v>-8.366315831693839</v>
+        <v>-8.914863295914456</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.67775245510635</v>
       </c>
       <c r="E70">
-        <v>-10.33286575760547</v>
+        <v>-8.729215371165198</v>
       </c>
       <c r="F70">
-        <v>4.952585873762769</v>
+        <v>4.639707349402636</v>
       </c>
       <c r="G70">
-        <v>-8.866194965941631</v>
+        <v>-8.072948528185783</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.486089871790339</v>
       </c>
       <c r="E71">
-        <v>-9.40205603922486</v>
+        <v>-10.00065237592877</v>
       </c>
       <c r="F71">
-        <v>5.092785023632961</v>
+        <v>4.851146342467041</v>
       </c>
       <c r="G71">
-        <v>-8.388820920269804</v>
+        <v>-8.649880609860112</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.278884827270392</v>
       </c>
       <c r="E72">
-        <v>-9.262909618391172</v>
+        <v>-9.665762666113528</v>
       </c>
       <c r="F72">
-        <v>4.822544613634205</v>
+        <v>4.657888293311881</v>
       </c>
       <c r="G72">
-        <v>-8.089348970787333</v>
+        <v>-8.218109328991746</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.059859244213278</v>
       </c>
       <c r="E73">
-        <v>-10.5369776665532</v>
+        <v>-9.212100140025111</v>
       </c>
       <c r="F73">
-        <v>4.391890631460587</v>
+        <v>4.070352403154832</v>
       </c>
       <c r="G73">
-        <v>-8.135987936344586</v>
+        <v>-8.164865825083648</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.829205652638449</v>
       </c>
       <c r="E74">
-        <v>-9.779676429776476</v>
+        <v>-9.973988720971603</v>
       </c>
       <c r="F74">
-        <v>4.87097909164609</v>
+        <v>4.329852119635078</v>
       </c>
       <c r="G74">
-        <v>-7.767683124009587</v>
+        <v>-8.068707719349977</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.593886034724202</v>
       </c>
       <c r="E75">
-        <v>-10.20236872212643</v>
+        <v>-9.746591398676436</v>
       </c>
       <c r="F75">
-        <v>4.75469865221678</v>
+        <v>4.006719099472474</v>
       </c>
       <c r="G75">
-        <v>-8.360999095557769</v>
+        <v>-8.726880588558021</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.351715562731886</v>
       </c>
       <c r="E76">
-        <v>-10.48594629296076</v>
+        <v>-8.851407185314168</v>
       </c>
       <c r="F76">
-        <v>4.312600811098195</v>
+        <v>4.181381273768545</v>
       </c>
       <c r="G76">
-        <v>-8.18457350267893</v>
+        <v>-8.456183900902895</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.107725173323098</v>
       </c>
       <c r="E77">
-        <v>-11.40961913630528</v>
+        <v>-10.22316800324366</v>
       </c>
       <c r="F77">
-        <v>4.533790681483961</v>
+        <v>3.522660970124323</v>
       </c>
       <c r="G77">
-        <v>-8.24589473770285</v>
+        <v>-7.063688993992491</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.862494615810194</v>
       </c>
       <c r="E78">
-        <v>-11.02004810284742</v>
+        <v>-10.37264840176285</v>
       </c>
       <c r="F78">
-        <v>4.21875198225517</v>
+        <v>3.735466701393752</v>
       </c>
       <c r="G78">
-        <v>-7.477570086766636</v>
+        <v>-7.356662342581373</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.618144677612962</v>
       </c>
       <c r="E79">
-        <v>-11.40655335940209</v>
+        <v>-12.01777961011339</v>
       </c>
       <c r="F79">
-        <v>4.177501194275719</v>
+        <v>3.617170204334087</v>
       </c>
       <c r="G79">
-        <v>-7.662861320599644</v>
+        <v>-6.70357116077611</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.37860702131908</v>
       </c>
       <c r="E80">
-        <v>-12.55908169367225</v>
+        <v>-12.20046278005682</v>
       </c>
       <c r="F80">
-        <v>4.247738551625457</v>
+        <v>3.370511175416224</v>
       </c>
       <c r="G80">
-        <v>-7.229484425144731</v>
+        <v>-6.809005415110819</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.145717951749548</v>
       </c>
       <c r="E81">
-        <v>-13.27825317930439</v>
+        <v>-10.97548791861195</v>
       </c>
       <c r="F81">
-        <v>4.059497682810409</v>
+        <v>3.534690800258001</v>
       </c>
       <c r="G81">
-        <v>-6.270555114784979</v>
+        <v>-7.898731069181637</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.9291965574409</v>
       </c>
       <c r="E82">
-        <v>-13.52519992389067</v>
+        <v>-13.05721836299</v>
       </c>
       <c r="F82">
-        <v>4.148150372544879</v>
+        <v>3.404214021002691</v>
       </c>
       <c r="G82">
-        <v>-5.572708667834308</v>
+        <v>-6.826058035183605</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.733780614406933</v>
       </c>
       <c r="E83">
-        <v>-14.88923969363709</v>
+        <v>-13.18283823196277</v>
       </c>
       <c r="F83">
-        <v>4.271742782185774</v>
+        <v>3.684330421090128</v>
       </c>
       <c r="G83">
-        <v>-6.090388605446762</v>
+        <v>-7.036042628194037</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.572245576147383</v>
       </c>
       <c r="E84">
-        <v>-15.62760285211373</v>
+        <v>-14.10825000932624</v>
       </c>
       <c r="F84">
-        <v>3.957988468454403</v>
+        <v>3.561257466989498</v>
       </c>
       <c r="G84">
-        <v>-5.524841489881986</v>
+        <v>-6.331955802901841</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.452339914751017</v>
       </c>
       <c r="E85">
-        <v>-17.02848175791255</v>
+        <v>-15.98561947868614</v>
       </c>
       <c r="F85">
-        <v>4.08798696852325</v>
+        <v>3.401754525716014</v>
       </c>
       <c r="G85">
-        <v>-5.710854422642556</v>
+        <v>-7.00228168478455</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.386901006758123</v>
       </c>
       <c r="E86">
-        <v>-18.49823422489402</v>
+        <v>-17.10066563359481</v>
       </c>
       <c r="F86">
-        <v>4.267826277456892</v>
+        <v>3.193950137727542</v>
       </c>
       <c r="G86">
-        <v>-5.663235535605679</v>
+        <v>-5.930115164254026</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.383483584685051</v>
       </c>
       <c r="E87">
-        <v>-18.8635507515668</v>
+        <v>-17.83371236358645</v>
       </c>
       <c r="F87">
-        <v>3.714563367015867</v>
+        <v>3.080681906949397</v>
       </c>
       <c r="G87">
-        <v>-4.635595852578353</v>
+        <v>-4.78596414151759</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.451907902586107</v>
       </c>
       <c r="E88">
-        <v>-19.9991018367822</v>
+        <v>-18.23389361164428</v>
       </c>
       <c r="F88">
-        <v>3.616804368267621</v>
+        <v>3.076228525915182</v>
       </c>
       <c r="G88">
-        <v>-4.931631455791061</v>
+        <v>-5.155997058624087</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.599338831781535</v>
       </c>
       <c r="E89">
-        <v>-22.10172213175763</v>
+        <v>-20.40803209662285</v>
       </c>
       <c r="F89">
-        <v>3.503354011309201</v>
+        <v>3.153807943888898</v>
       </c>
       <c r="G89">
-        <v>-4.5142842218373</v>
+        <v>-5.14821396606126</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.827927946626704</v>
       </c>
       <c r="E90">
-        <v>-22.24500304936032</v>
+        <v>-22.22345204155782</v>
       </c>
       <c r="F90">
-        <v>3.673767102634147</v>
+        <v>2.653363209433695</v>
       </c>
       <c r="G90">
-        <v>-3.66340118624274</v>
+        <v>-3.636698325922979</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.142240684677821</v>
       </c>
       <c r="E91">
-        <v>-25.3586278089182</v>
+        <v>-23.80123125599227</v>
       </c>
       <c r="F91">
-        <v>3.02162234595083</v>
+        <v>2.677768117590617</v>
       </c>
       <c r="G91">
-        <v>-3.686922612299262</v>
+        <v>-3.867648603833616</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.534817418174149</v>
       </c>
       <c r="E92">
-        <v>-26.64176639051759</v>
+        <v>-24.94731104327551</v>
       </c>
       <c r="F92">
-        <v>3.202988347386955</v>
+        <v>2.579910929075613</v>
       </c>
       <c r="G92">
-        <v>-3.659627164327971</v>
+        <v>-3.62370443468134</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.004556702012152</v>
       </c>
       <c r="E93">
-        <v>-29.36329775659533</v>
+        <v>-27.67796728447871</v>
       </c>
       <c r="F93">
-        <v>3.13640618329005</v>
+        <v>2.430852528314452</v>
       </c>
       <c r="G93">
-        <v>-3.807582065569079</v>
+        <v>-3.960982814222288</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.533862125031679</v>
       </c>
       <c r="E94">
-        <v>-31.66627359132913</v>
+        <v>-30.80608316086114</v>
       </c>
       <c r="F94">
-        <v>2.922164030755316</v>
+        <v>2.192029676266184</v>
       </c>
       <c r="G94">
-        <v>-2.874018155131222</v>
+        <v>-3.510675788879543</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.111756525286641</v>
       </c>
       <c r="E95">
-        <v>-33.23138213549012</v>
+        <v>-31.84070135315658</v>
       </c>
       <c r="F95">
-        <v>2.494075652164711</v>
+        <v>2.083089713754935</v>
       </c>
       <c r="G95">
-        <v>-4.667598896306488</v>
+        <v>-4.348359679409028</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.723544268549478</v>
       </c>
       <c r="E96">
-        <v>-35.09971277073071</v>
+        <v>-33.88653458407582</v>
       </c>
       <c r="F96">
-        <v>2.291682787289295</v>
+        <v>1.623000973436959</v>
       </c>
       <c r="G96">
-        <v>-3.360125419935646</v>
+        <v>-4.403900701921381</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.344666043154568</v>
       </c>
       <c r="E97">
-        <v>-37.52755674775201</v>
+        <v>-37.13631017891131</v>
       </c>
       <c r="F97">
-        <v>2.21019636682219</v>
+        <v>1.328040497804108</v>
       </c>
       <c r="G97">
-        <v>-3.847444344407443</v>
+        <v>-3.120273085069909</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.975534511794663</v>
       </c>
       <c r="E98">
-        <v>-40.05557283405998</v>
+        <v>-37.76346080847058</v>
       </c>
       <c r="F98">
-        <v>1.600860764739116</v>
+        <v>1.288539704861218</v>
       </c>
       <c r="G98">
-        <v>-3.114572325651285</v>
+        <v>-3.549594562239215</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.583658981179584</v>
       </c>
       <c r="E99">
-        <v>-41.77196410939521</v>
+        <v>-41.26550863332537</v>
       </c>
       <c r="F99">
-        <v>1.154973115364886</v>
+        <v>0.8814465155915925</v>
       </c>
       <c r="G99">
-        <v>-3.584699587137647</v>
+        <v>-3.407611885150952</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.19532566586385</v>
       </c>
       <c r="E100">
-        <v>-44.99503529300747</v>
+        <v>-42.74100320534858</v>
       </c>
       <c r="F100">
-        <v>1.111120298566368</v>
+        <v>0.4949755528998618</v>
       </c>
       <c r="G100">
-        <v>-4.100995716714684</v>
+        <v>-4.890872019111554</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.76191681324259</v>
       </c>
       <c r="E101">
-        <v>-47.45780739004993</v>
+        <v>-44.84288083058675</v>
       </c>
       <c r="F101">
-        <v>1.028520532840708</v>
+        <v>0.9014946487751404</v>
       </c>
       <c r="G101">
-        <v>-4.348856261239918</v>
+        <v>-3.92081927573985</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.35999379825065</v>
       </c>
       <c r="E102">
-        <v>-48.95458012931667</v>
+        <v>-48.76522085656743</v>
       </c>
       <c r="F102">
-        <v>0.622767158775544</v>
+        <v>-0.0391894479068785</v>
       </c>
       <c r="G102">
-        <v>-3.633712213846557</v>
+        <v>-4.657428900409847</v>
       </c>
     </row>
   </sheetData>
